--- a/backend/app/templates/Planilla_Logistica_Eventos.xlsx
+++ b/backend/app/templates/Planilla_Logistica_Eventos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karen\Downloads\logistica\backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A2B75D-EFB3-4736-89D5-2769EB002288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53668A79-A009-4147-8824-BC008629421A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,50 +109,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="2" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,7 +127,12 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,7 +140,15 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
+      <sz val="18"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -360,19 +332,72 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -384,102 +409,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,538 +788,540 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:N36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" customWidth="1"/>
-    <col min="5" max="5" width="31.42578125" customWidth="1"/>
-    <col min="6" max="6" width="39.85546875" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" customWidth="1"/>
-    <col min="12" max="12" width="26.140625" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="6" style="2" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="39.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="39.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24" style="2" customWidth="1"/>
+    <col min="9" max="10" width="12" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="26.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="36" t="s">
+    <row r="2" spans="2:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="30" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="26" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="2:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="39" t="s">
+      <c r="L2" s="29"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="2:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="33" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="14"/>
-      <c r="C5" s="21" t="s">
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="10"/>
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="21" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="L5" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="20"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="15"/>
-      <c r="C6" s="21" t="s">
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="11"/>
+      <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="23" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="6" t="s">
+      <c r="I6" s="18"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="16"/>
-      <c r="C7" s="21" t="s">
+      <c r="L6" s="14"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="12"/>
+      <c r="C7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="23" t="s">
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
+      <c r="J7" s="17"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="22" t="s">
+      <c r="L8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
+    <row r="9" spans="2:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+    </row>
+    <row r="10" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="5">
         <v>2</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+    </row>
+    <row r="11" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="5">
         <v>3</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="5">
         <v>4</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="5">
         <v>5</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="5">
         <v>6</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="5">
         <v>7</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="1">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="2:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="5">
         <v>8</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="5">
         <v>9</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="1">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="5">
         <v>10</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="1">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="5">
         <v>11</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="1">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="5">
         <v>12</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="1">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="5">
         <v>13</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="5">
         <v>14</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-    </row>
-    <row r="23" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="1">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="5">
         <v>15</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="1">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="5">
         <v>16</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-    </row>
-    <row r="25" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="1">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="5">
         <v>17</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-    </row>
-    <row r="26" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="1">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="2:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="5">
         <v>18</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-    </row>
-    <row r="27" spans="2:13" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="1">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="2:13" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="5">
         <v>19</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-    </row>
-    <row r="28" spans="2:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="1">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+    </row>
+    <row r="28" spans="2:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="5">
         <v>20</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="2:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="6"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1394,8 +1342,9 @@
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="D2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="39" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.98425196850393704" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.39370078740157483"/>
+  <pageSetup scale="42" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>